--- a/Report/Demo_Attendance_Import_Session.xlsx
+++ b/Report/Demo_Attendance_Import_Session.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điểm danh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attendance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,13 +28,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
+      <color rgb="001F497D"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00475569"/>
+      <color rgb="00595959"/>
       <sz val="10"/>
     </font>
     <font>
@@ -45,10 +45,10 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +57,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00DCE6F1"/>
+        <bgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,16 +84,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
@@ -96,20 +102,20 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,17 +485,17 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BẢNG ĐIỂM DANH - Flight Operations Briefing - AMT-101-C1</t>
+          <t>ATTENDANCE SHEET - Flight Operations Briefing - AMT-101-C1</t>
         </is>
       </c>
     </row>
@@ -511,16 +517,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ngày: 15/09/2026</t>
+          <t>Date: 15/09/2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Môn: Aviation Regulations</t>
+          <t>Subject: Aviation Regulations</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>EnrollmentId</t>
@@ -528,22 +534,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Họ và tên</t>
+          <t>Full Name</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Mã học viên</t>
+          <t>Student Code</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Trạng thái (Present/Absent)*</t>
+          <t>Status (Present/Absent)*</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Ghi chú</t>
+          <t>Remarks</t>
         </is>
       </c>
     </row>
@@ -551,7 +557,7 @@
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Jane Student</t>
         </is>
@@ -561,14 +567,14 @@
           <t>STU-01</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Đúng giờ, chuẩn bị bài tốt</t>
+          <t>On time, well prepared</t>
         </is>
       </c>
     </row>
@@ -576,7 +582,7 @@
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Student 2</t>
         </is>
@@ -586,14 +592,14 @@
           <t>STU-02</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Có mặt đầy đủ</t>
+          <t>Present and attentive</t>
         </is>
       </c>
     </row>
@@ -601,7 +607,7 @@
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Student 3</t>
         </is>
@@ -611,14 +617,14 @@
           <t>STU-03</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Có mặt đầy đủ</t>
+          <t>Present and attentive</t>
         </is>
       </c>
     </row>
@@ -626,7 +632,7 @@
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Student 4</t>
         </is>
@@ -636,14 +642,14 @@
           <t>STU-04</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Nghỉ có phép (kiểm tra sức khỏe định kỳ)</t>
+          <t>Excused absence (Routine medical examination)</t>
         </is>
       </c>
     </row>

--- a/Report/Demo_Attendance_Import_Session.xlsx
+++ b/Report/Demo_Attendance_Import_Session.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Date: 15/09/2026</t>
+          <t>Date: 15/10/2026</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
